--- a/assets/COF_Data_Sample.xlsx
+++ b/assets/COF_Data_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Career\AI Models\Claude\ERR Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8496AF88-DFE2-42F3-AD5D-C5C47CD9A475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBD1DA4-3FFB-4CF2-9D27-AFB97FDA66F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Year</t>
   </si>
@@ -47,19 +47,22 @@
     <t>Day</t>
   </si>
   <si>
-    <t>COF</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Do Not Input Here</t>
+    <t>ISC</t>
   </si>
   <si>
-    <t>Do Not Input</t>
+    <t>Eligible COF</t>
   </si>
   <si>
-    <t>Input</t>
+    <t>COF (M-o-M)</t>
+  </si>
+  <si>
+    <t>Do Not Edit</t>
+  </si>
+  <si>
+    <t>Input Required</t>
   </si>
 </sst>
 </file>
@@ -67,9 +70,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +82,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,31 +145,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -159,16 +213,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF4B84F0-4B37-4242-A8C1-82524EFF114B}" name="Table1" displayName="Table1" ref="A4:E9" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A4:E9" xr:uid="{DF4B84F0-4B37-4242-A8C1-82524EFF114B}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A158132F-AFE8-4719-ACF6-8984BCC724DF}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{E61BB3FC-A959-411E-9980-C38975A0A065}" name="Month"/>
-    <tableColumn id="3" xr3:uid="{74A54D62-EFAE-45D0-897C-F0C9D5DE103F}" name="Day"/>
-    <tableColumn id="4" xr3:uid="{98A0F5A8-2D1B-4E37-92F9-CB5A790C0295}" name="Date" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:G32" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A3:G32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Day"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Date" dataDxfId="3">
       <calculatedColumnFormula>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{452B879F-2638-46AE-B5B7-301A86C31FC0}" name="COF" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="COF (M-o-M)" dataDxfId="2" dataCellStyle="Percent"/>
+    <tableColumn id="6" xr3:uid="{7D7FC888-124E-4B22-8EDC-00D52619BD80}" name="ISC" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="7" xr3:uid="{6FE2EDEA-AEA6-450D-BEBD-BDA95487BAB9}" name="Eligible COF" dataDxfId="0">
+      <calculatedColumnFormula>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -437,135 +495,779 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultColWidth="19.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45292</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.10290000000000001</v>
+      </c>
+      <c r="G4" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.10590000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45323</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.1055</v>
+      </c>
+      <c r="G5" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1085</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45352</v>
+      </c>
+      <c r="E6" s="2">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.10879999999999999</v>
+      </c>
+      <c r="G6" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2020</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>43831</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2021</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5">
-        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>44228</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2022</v>
-      </c>
-      <c r="B7">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45383</v>
+      </c>
+      <c r="E7" s="2">
+        <v>9.9099999999999994E-2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.1115</v>
+      </c>
+      <c r="G7" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8">
         <v>5</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
-        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>44682</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2022</v>
-      </c>
-      <c r="B8">
-        <v>9</v>
-      </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="5">
-        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>44805</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45413</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.1026</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="G8" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2024</v>
       </c>
       <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45444</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.1048</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.1235</v>
+      </c>
+      <c r="G9" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45474</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.1074</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.1235</v>
+      </c>
+      <c r="G10" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45505</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.112</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.1235</v>
+      </c>
+      <c r="G11" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45536</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.11409999999999999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.1225</v>
+      </c>
+      <c r="G12" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13">
         <v>10</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
         <v>45566</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E13" s="2">
+        <v>0.1149</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.1225</v>
+      </c>
+      <c r="G13" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45597</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.1225</v>
+      </c>
+      <c r="G14" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45627</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.1222</v>
+      </c>
+      <c r="G15" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.12520000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2025</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45658</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.1172</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.12189999999999999</v>
+      </c>
+      <c r="G16" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45689</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.1181</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.121</v>
+      </c>
+      <c r="G17" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2025</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45717</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.1182</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.121</v>
+      </c>
+      <c r="G18" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2025</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45748</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="F19" s="2">
         <v>0.12</v>
       </c>
+      <c r="G19" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2025</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45778</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G20" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2025</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45809</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G21" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2025</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45839</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.11849999999999999</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G22" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2025</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45870</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.1181</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.11849999999999999</v>
+      </c>
+      <c r="G23" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2025</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45901</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.11749999999999999</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="G24" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2025</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45931</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.1166</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.111</v>
+      </c>
+      <c r="G25" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2025</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45962</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.11509999999999999</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.107</v>
+      </c>
+      <c r="G26" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2025</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45992</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.1132</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.1071</v>
+      </c>
+      <c r="G27" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2026</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46023</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.1116</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.1069</v>
+      </c>
+      <c r="G28" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.11460000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46054</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.1103</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.1067</v>
+      </c>
+      <c r="G29" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2026</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46082</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.1089</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="G30" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2026</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46113</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.108</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.1055</v>
+      </c>
+      <c r="G31" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2026</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46143</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.1072</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.1062</v>
+      </c>
+      <c r="G32" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.11020000000000001</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/assets/COF_Data_Sample.xlsx
+++ b/assets/COF_Data_Sample.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Career\AI Models\Claude\ERR Calculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imahfuzul\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBD1DA4-3FFB-4CF2-9D27-AFB97FDA66F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,7 +67,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -160,10 +159,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -194,7 +193,6 @@
         <sz val="14"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -213,18 +211,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:G32" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A3:G32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:G56" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A3:G56"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Day"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Date" dataDxfId="3">
+    <tableColumn id="1" name="Year"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Day"/>
+    <tableColumn id="4" name="Date" dataDxfId="3">
       <calculatedColumnFormula>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="COF (M-o-M)" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="6" xr3:uid="{7D7FC888-124E-4B22-8EDC-00D52619BD80}" name="ISC" dataDxfId="1" dataCellStyle="Percent"/>
-    <tableColumn id="7" xr3:uid="{6FE2EDEA-AEA6-450D-BEBD-BDA95487BAB9}" name="Eligible COF" dataDxfId="0">
+    <tableColumn id="5" name="COF (M-o-M)" dataDxfId="2" dataCellStyle="Percent"/>
+    <tableColumn id="6" name="ISC" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="7" name="Eligible COF" dataDxfId="0">
       <calculatedColumnFormula>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -494,23 +492,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="19.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="7"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
@@ -540,7 +538,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -550,22 +548,22 @@
       </c>
       <c r="D4" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45292</v>
+        <v>44562</v>
       </c>
       <c r="E4" s="2">
-        <v>8.9899999999999994E-2</v>
+        <v>6.0299999999999999E-2</v>
       </c>
       <c r="F4" s="2">
-        <v>0.10290000000000001</v>
+        <v>6.3299999999999995E-2</v>
       </c>
       <c r="G4" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.10590000000000001</v>
+        <v>6.6299999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -575,22 +573,22 @@
       </c>
       <c r="D5" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45323</v>
+        <v>44593</v>
       </c>
       <c r="E5" s="2">
-        <v>9.2700000000000005E-2</v>
+        <v>6.1499999999999999E-2</v>
       </c>
       <c r="F5" s="2">
-        <v>0.1055</v>
+        <v>6.4199999999999993E-2</v>
       </c>
       <c r="G5" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1085</v>
+        <v>6.7199999999999996E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -600,22 +598,22 @@
       </c>
       <c r="D6" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45352</v>
+        <v>44621</v>
       </c>
       <c r="E6" s="2">
-        <v>9.6000000000000002E-2</v>
+        <v>6.2100000000000002E-2</v>
       </c>
       <c r="F6" s="2">
-        <v>0.10879999999999999</v>
+        <v>6.7299999999999999E-2</v>
       </c>
       <c r="G6" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1118</v>
+        <v>7.0300000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -625,22 +623,22 @@
       </c>
       <c r="D7" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45383</v>
+        <v>44652</v>
       </c>
       <c r="E7" s="2">
-        <v>9.9099999999999994E-2</v>
+        <v>6.3100000000000003E-2</v>
       </c>
       <c r="F7" s="2">
-        <v>0.1115</v>
+        <v>6.9900000000000004E-2</v>
       </c>
       <c r="G7" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1145</v>
+        <v>7.2900000000000006E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -650,22 +648,22 @@
       </c>
       <c r="D8" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45413</v>
+        <v>44682</v>
       </c>
       <c r="E8" s="2">
-        <v>0.1026</v>
+        <v>6.3899999999999998E-2</v>
       </c>
       <c r="F8" s="2">
-        <v>0.11899999999999999</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="G8" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.122</v>
+        <v>7.2500000000000009E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -675,22 +673,22 @@
       </c>
       <c r="D9" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45444</v>
+        <v>44713</v>
       </c>
       <c r="E9" s="2">
-        <v>0.1048</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="F9" s="2">
-        <v>0.1235</v>
+        <v>7.0099999999999996E-2</v>
       </c>
       <c r="G9" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1265</v>
+        <v>7.3099999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -700,22 +698,22 @@
       </c>
       <c r="D10" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45474</v>
+        <v>44743</v>
       </c>
       <c r="E10" s="2">
-        <v>0.1074</v>
+        <v>6.5799999999999997E-2</v>
       </c>
       <c r="F10" s="2">
-        <v>0.1235</v>
+        <v>6.9800000000000001E-2</v>
       </c>
       <c r="G10" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1265</v>
+        <v>7.2800000000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -725,22 +723,22 @@
       </c>
       <c r="D11" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45505</v>
+        <v>44774</v>
       </c>
       <c r="E11" s="2">
-        <v>0.112</v>
+        <v>6.6900000000000001E-2</v>
       </c>
       <c r="F11" s="2">
-        <v>0.1235</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="G11" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1265</v>
+        <v>7.2500000000000009E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -750,22 +748,22 @@
       </c>
       <c r="D12" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45536</v>
+        <v>44805</v>
       </c>
       <c r="E12" s="2">
-        <v>0.11409999999999999</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="F12" s="2">
-        <v>0.1225</v>
+        <v>7.2700000000000001E-2</v>
       </c>
       <c r="G12" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1255</v>
+        <v>7.5700000000000003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -775,22 +773,22 @@
       </c>
       <c r="D13" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45566</v>
+        <v>44835</v>
       </c>
       <c r="E13" s="2">
-        <v>0.1149</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="F13" s="2">
-        <v>0.1225</v>
+        <v>6.9800000000000001E-2</v>
       </c>
       <c r="G13" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1255</v>
+        <v>7.2800000000000004E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B14">
         <v>11</v>
@@ -800,22 +798,22 @@
       </c>
       <c r="D14" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45597</v>
+        <v>44866</v>
       </c>
       <c r="E14" s="2">
-        <v>0.11600000000000001</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="F14" s="2">
-        <v>0.1225</v>
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="G14" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1255</v>
+        <v>7.4499999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B15">
         <v>12</v>
@@ -825,22 +823,22 @@
       </c>
       <c r="D15" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="E15" s="2">
-        <v>0.11650000000000001</v>
+        <v>6.93E-2</v>
       </c>
       <c r="F15" s="2">
-        <v>0.1222</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="G15" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.12520000000000001</v>
+        <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -850,22 +848,22 @@
       </c>
       <c r="D16" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45658</v>
+        <v>44927</v>
       </c>
       <c r="E16" s="2">
-        <v>0.1172</v>
+        <v>6.9800000000000001E-2</v>
       </c>
       <c r="F16" s="2">
-        <v>0.12189999999999999</v>
+        <v>7.2300000000000003E-2</v>
       </c>
       <c r="G16" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1249</v>
+        <v>7.5300000000000006E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -875,22 +873,22 @@
       </c>
       <c r="D17" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45689</v>
+        <v>44958</v>
       </c>
       <c r="E17" s="2">
-        <v>0.1181</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="F17" s="2">
-        <v>0.121</v>
+        <v>7.0900000000000005E-2</v>
       </c>
       <c r="G17" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.124</v>
+        <v>7.3900000000000007E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -900,22 +898,22 @@
       </c>
       <c r="D18" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45717</v>
+        <v>44986</v>
       </c>
       <c r="E18" s="2">
-        <v>0.1182</v>
+        <v>7.1599999999999997E-2</v>
       </c>
       <c r="F18" s="2">
-        <v>0.121</v>
+        <v>7.9200000000000007E-2</v>
       </c>
       <c r="G18" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.124</v>
+        <v>8.2200000000000009E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -925,22 +923,22 @@
       </c>
       <c r="D19" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45748</v>
+        <v>45017</v>
       </c>
       <c r="E19" s="2">
-        <v>0.11799999999999999</v>
+        <v>7.3099999999999998E-2</v>
       </c>
       <c r="F19" s="2">
-        <v>0.12</v>
+        <v>7.8899999999999998E-2</v>
       </c>
       <c r="G19" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.123</v>
+        <v>8.1900000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -950,22 +948,22 @@
       </c>
       <c r="D20" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45778</v>
+        <v>45047</v>
       </c>
       <c r="E20" s="2">
-        <v>0.11840000000000001</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F20" s="2">
-        <v>0.12</v>
+        <v>7.7899999999999997E-2</v>
       </c>
       <c r="G20" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.123</v>
+        <v>8.09E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -975,22 +973,22 @@
       </c>
       <c r="D21" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45809</v>
+        <v>45078</v>
       </c>
       <c r="E21" s="2">
-        <v>0.11840000000000001</v>
+        <v>7.5499999999999998E-2</v>
       </c>
       <c r="F21" s="2">
-        <v>0.12</v>
+        <v>7.9299999999999995E-2</v>
       </c>
       <c r="G21" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.123</v>
+        <v>8.2299999999999998E-2</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B22">
         <v>7</v>
@@ -1000,22 +998,22 @@
       </c>
       <c r="D22" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45839</v>
+        <v>45108</v>
       </c>
       <c r="E22" s="2">
-        <v>0.11849999999999999</v>
+        <v>7.6899999999999996E-2</v>
       </c>
       <c r="F22" s="2">
-        <v>0.12</v>
+        <v>8.4400000000000003E-2</v>
       </c>
       <c r="G22" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.123</v>
+        <v>8.7400000000000005E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -1025,22 +1023,22 @@
       </c>
       <c r="D23" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45870</v>
+        <v>45139</v>
       </c>
       <c r="E23" s="2">
-        <v>0.1181</v>
+        <v>7.7899999999999997E-2</v>
       </c>
       <c r="F23" s="2">
-        <v>0.11849999999999999</v>
+        <v>8.3799999999999999E-2</v>
       </c>
       <c r="G23" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1215</v>
+        <v>8.6800000000000002E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B24">
         <v>9</v>
@@ -1050,22 +1048,22 @@
       </c>
       <c r="D24" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45901</v>
+        <v>45170</v>
       </c>
       <c r="E24" s="2">
-        <v>0.11749999999999999</v>
+        <v>7.8299999999999995E-2</v>
       </c>
       <c r="F24" s="2">
-        <v>0.11600000000000001</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="G24" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1205</v>
+        <v>8.6000000000000007E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -1075,22 +1073,22 @@
       </c>
       <c r="D25" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45931</v>
+        <v>45200</v>
       </c>
       <c r="E25" s="2">
-        <v>0.1166</v>
+        <v>8.0199999999999994E-2</v>
       </c>
       <c r="F25" s="2">
-        <v>0.111</v>
+        <v>8.7400000000000005E-2</v>
       </c>
       <c r="G25" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1196</v>
+        <v>9.0400000000000008E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B26">
         <v>11</v>
@@ -1100,22 +1098,22 @@
       </c>
       <c r="D26" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45962</v>
+        <v>45231</v>
       </c>
       <c r="E26" s="2">
-        <v>0.11509999999999999</v>
+        <v>8.3400000000000002E-2</v>
       </c>
       <c r="F26" s="2">
-        <v>0.107</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="G26" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1181</v>
+        <v>9.5799999999999996E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B27">
         <v>12</v>
@@ -1125,22 +1123,22 @@
       </c>
       <c r="D27" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>45992</v>
+        <v>45261</v>
       </c>
       <c r="E27" s="2">
-        <v>0.1132</v>
+        <v>8.6099999999999996E-2</v>
       </c>
       <c r="F27" s="2">
-        <v>0.1071</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="G27" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1162</v>
+        <v>0.1009</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1150,22 +1148,22 @@
       </c>
       <c r="D28" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>46023</v>
+        <v>45292</v>
       </c>
       <c r="E28" s="2">
-        <v>0.1116</v>
+        <v>8.9899999999999994E-2</v>
       </c>
       <c r="F28" s="2">
-        <v>0.1069</v>
+        <v>0.10290000000000001</v>
       </c>
       <c r="G28" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.11460000000000001</v>
+        <v>0.10590000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -1175,22 +1173,22 @@
       </c>
       <c r="D29" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>46054</v>
+        <v>45323</v>
       </c>
       <c r="E29" s="2">
-        <v>0.1103</v>
+        <v>9.2700000000000005E-2</v>
       </c>
       <c r="F29" s="2">
-        <v>0.1067</v>
+        <v>0.1055</v>
       </c>
       <c r="G29" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1133</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -1200,22 +1198,22 @@
       </c>
       <c r="D30" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>46082</v>
+        <v>45352</v>
       </c>
       <c r="E30" s="2">
-        <v>0.1089</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="F30" s="2">
-        <v>0.10589999999999999</v>
+        <v>0.10879999999999999</v>
       </c>
       <c r="G30" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.1119</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -1225,22 +1223,22 @@
       </c>
       <c r="D31" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
-        <v>46113</v>
+        <v>45383</v>
       </c>
       <c r="E31" s="2">
-        <v>0.108</v>
+        <v>9.9099999999999994E-2</v>
       </c>
       <c r="F31" s="2">
-        <v>0.1055</v>
+        <v>0.1115</v>
       </c>
       <c r="G31" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
-        <v>0.111</v>
+        <v>0.1145</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B32">
         <v>5</v>
@@ -1250,15 +1248,615 @@
       </c>
       <c r="D32" s="1">
         <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45413</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.1026</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="G32" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2024</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45444</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.1048</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.1235</v>
+      </c>
+      <c r="G33" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1265</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2024</v>
+      </c>
+      <c r="B34">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45474</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.1074</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.1235</v>
+      </c>
+      <c r="G34" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2024</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45505</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.112</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.1235</v>
+      </c>
+      <c r="G35" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1265</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2024</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45536</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.11409999999999999</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.1225</v>
+      </c>
+      <c r="G36" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2024</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45566</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.1149</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.1225</v>
+      </c>
+      <c r="G37" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2024</v>
+      </c>
+      <c r="B38">
+        <v>11</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45597</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.1225</v>
+      </c>
+      <c r="G38" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2024</v>
+      </c>
+      <c r="B39">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45627</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0.1222</v>
+      </c>
+      <c r="G39" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.12520000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2025</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45658</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.1172</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.12189999999999999</v>
+      </c>
+      <c r="G40" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2025</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45689</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.1181</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.121</v>
+      </c>
+      <c r="G41" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2025</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45717</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.1182</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.121</v>
+      </c>
+      <c r="G42" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2025</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45748</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G43" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2025</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45778</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G44" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2025</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45809</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G45" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45839</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.11849999999999999</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G46" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45870</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.1181</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.11849999999999999</v>
+      </c>
+      <c r="G47" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45901</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.11749999999999999</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="G48" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2025</v>
+      </c>
+      <c r="B49">
+        <v>10</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45931</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.1166</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.111</v>
+      </c>
+      <c r="G49" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2025</v>
+      </c>
+      <c r="B50">
+        <v>11</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45962</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.11509999999999999</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0.107</v>
+      </c>
+      <c r="G50" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2025</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>45992</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.1132</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0.1071</v>
+      </c>
+      <c r="G51" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1162</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2026</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46023</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0.1116</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0.1069</v>
+      </c>
+      <c r="G52" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.11460000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2026</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46054</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0.1103</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0.1067</v>
+      </c>
+      <c r="G53" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2026</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46082</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.1089</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="G54" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.1119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2026</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
+        <v>46113</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0.108</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0.1055</v>
+      </c>
+      <c r="G55" s="3">
+        <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2026</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" s="1">
+        <f>IFERROR(DATE(Table1[[#This Row],[Year]],Table1[[#This Row],[Month]],Table1[[#This Row],[Day]]),"")</f>
         <v>46143</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E56" s="2">
         <v>0.1072</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F56" s="2">
         <v>0.1062</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G56" s="3">
         <f>MAX(Table1[[#This Row],[COF (M-o-M)]:[ISC]])+0.3%</f>
         <v>0.11020000000000001</v>
       </c>
@@ -1269,8 +1867,9 @@
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>